--- a/src/nodes/HPC/compressor_stage_8_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_8_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>7.2291451102383748</v>
+        <v>6.8401430258888</v>
       </c>
       <c r="B1">
-        <v>8.3131681900657419</v>
+        <v>8.6360724734446919</v>
       </c>
       <c r="C1">
         <v>194.11826296981104</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>6.5639096099648579</v>
+        <v>6.182985734500317</v>
       </c>
       <c r="B2">
-        <v>8.1523551710106759</v>
+        <v>8.44490921260016</v>
       </c>
       <c r="C2">
         <v>194.11826296981104</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>5.9608778035466479</v>
+        <v>5.5911896935945586</v>
       </c>
       <c r="B3">
-        <v>7.9212892051065582</v>
+        <v>8.1864207484098177</v>
       </c>
       <c r="C3">
         <v>194.11826296981104</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>5.3723359022476</v>
+        <v>5.0146190880169268</v>
       </c>
       <c r="B4">
-        <v>7.673858318229219</v>
+        <v>7.91224936013335</v>
       </c>
       <c r="C4">
         <v>194.11826296981104</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>4.795551416498447</v>
+        <v>4.4504027227609981</v>
       </c>
       <c r="B5">
-        <v>7.4131485882717545</v>
+        <v>7.6253525154786956</v>
       </c>
       <c r="C5">
         <v>194.11826296981104</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4.2293659076721912</v>
+        <v>3.8973233550462356</v>
       </c>
       <c r="B6">
-        <v>7.1404683575888708</v>
+        <v>7.3269840325279043</v>
       </c>
       <c r="C6">
         <v>194.11826296981104</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>3.6730917780447911</v>
+        <v>3.354658483614485</v>
       </c>
       <c r="B7">
-        <v>6.8565942001003268</v>
+        <v>7.0178881220138472</v>
       </c>
       <c r="C7">
         <v>194.11826296981104</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.1262989085046184</v>
+        <v>2.8219561558364057</v>
       </c>
       <c r="B8">
-        <v>6.5620118929877531</v>
+        <v>6.6985303166864059</v>
       </c>
       <c r="C8">
         <v>194.11826296981104</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.5883609673794874</v>
+        <v>2.2985582464661554</v>
       </c>
       <c r="B9">
-        <v>6.2574288161983613</v>
+        <v>6.3695885169173776</v>
       </c>
       <c r="C9">
         <v>194.11826296981104</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.0586101889704662</v>
+        <v>1.7837630929752437</v>
       </c>
       <c r="B10">
-        <v>5.9435991453324624</v>
+        <v>6.031785468554828</v>
       </c>
       <c r="C10">
         <v>194.11826296981104</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.5364092840321553</v>
+        <v>1.2769010563210896</v>
       </c>
       <c r="B11">
-        <v>5.6212426358371941</v>
+        <v>5.6858109317299821</v>
       </c>
       <c r="C11">
         <v>194.11826296981104</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.0213982330710072</v>
+        <v>0.77759384185850311</v>
       </c>
       <c r="B12">
-        <v>5.2907658942784561</v>
+        <v>5.3320545679582478</v>
       </c>
       <c r="C12">
         <v>194.11826296981104</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.51429561914732769</v>
+        <v>0.28659650904595479</v>
       </c>
       <c r="B13">
-        <v>4.9513573518503877</v>
+        <v>4.9697386300085933</v>
       </c>
       <c r="C13">
         <v>194.11826296981104</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>0.015518343624226251</v>
+        <v>-0.19565287818928706</v>
       </c>
       <c r="B14">
-        <v>4.6025461595167281</v>
+        <v>4.5984118911562568</v>
       </c>
       <c r="C14">
         <v>194.11826296981104</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.47680202147783268</v>
+        <v>-0.67111759214843791</v>
       </c>
       <c r="B15">
-        <v>4.2464425226913649</v>
+        <v>4.2200966154479955</v>
       </c>
       <c r="C15">
         <v>194.11826296981104</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.96437902216252747</v>
+        <v>-1.1415981611059209</v>
       </c>
       <c r="B16">
-        <v>3.8849817228480958</v>
+        <v>3.8366474328260196</v>
       </c>
       <c r="C16">
         <v>194.11826296981104</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.4460213471874708</v>
+        <v>-1.6058428010005252</v>
       </c>
       <c r="B17">
-        <v>3.5168182912501798</v>
+        <v>3.4467749460428205</v>
       </c>
       <c r="C17">
         <v>194.11826296981104</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-1.9201804266997287</v>
+        <v>-2.0622243341555824</v>
       </c>
       <c r="B18">
-        <v>3.1402032707404546</v>
+        <v>3.0488030845343825</v>
       </c>
       <c r="C18">
         <v>194.11826296981104</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-2.3867835136502462</v>
+        <v>-2.5106663207682383</v>
       </c>
       <c r="B19">
-        <v>2.755054500690608</v>
+        <v>2.6426531116603758</v>
       </c>
       <c r="C19">
         <v>194.11826296981104</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-2.8461268166909441</v>
+        <v>-2.9514800055040968</v>
       </c>
       <c r="B20">
-        <v>2.3617065196045361</v>
+        <v>2.228645624261389</v>
       </c>
       <c r="C20">
         <v>194.11826296981104</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.2985065444737369</v>
+        <v>-3.3849766330287556</v>
       </c>
       <c r="B21">
-        <v>1.9604938659861428</v>
+        <v>1.8071012191780169</v>
       </c>
       <c r="C21">
         <v>194.11826296981104</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-3.7441648957349813</v>
+        <v>-3.8114106964646068</v>
       </c>
       <c r="B22">
-        <v>1.5516900794581927</v>
+        <v>1.3782820364563611</v>
       </c>
       <c r="C22">
         <v>194.11826296981104</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.183128029548782</v>
+        <v>-4.2308096827612038</v>
       </c>
       <c r="B23">
-        <v>1.1353247041189376</v>
+        <v>0.94221638896458937</v>
       </c>
       <c r="C23">
         <v>194.11826296981104</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.6153680950736815</v>
+        <v>-4.6431443273248894</v>
       </c>
       <c r="B24">
-        <v>0.71136628518549738</v>
+        <v>0.49887413277638043</v>
       </c>
       <c r="C24">
         <v>194.11826296981104</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.0408572414682249</v>
+        <v>-5.048385365562007</v>
       </c>
       <c r="B25">
-        <v>0.27978336787499264</v>
+        <v>0.04822512396541459</v>
       </c>
       <c r="C25">
         <v>194.11826296981104</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.4595563948827177</v>
+        <v>-5.4464917401732418</v>
       </c>
       <c r="B26">
-        <v>-0.15946817787809664</v>
+        <v>-0.40977292844353397</v>
       </c>
       <c r="C26">
         <v>194.11826296981104</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.871381589434538</v>
+        <v>-5.8373752230366618</v>
       </c>
       <c r="B27">
-        <v>-0.60648318326986117</v>
+        <v>-0.87521090362133</v>
       </c>
       <c r="C27">
         <v>194.11826296981104</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.276237636232822</v>
+        <v>-6.2209357933246716</v>
       </c>
       <c r="B28">
-        <v>-1.0613691547790276</v>
+        <v>-1.3481918277877372</v>
       </c>
       <c r="C28">
         <v>194.11826296981104</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.67402934638671</v>
+        <v>-6.59707343020968</v>
       </c>
       <c r="B29">
-        <v>-1.5242335988843239</v>
+        <v>-1.828818727162524</v>
       </c>
       <c r="C29">
         <v>194.11826296981104</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.0646966411825147</v>
+        <v>-6.9657250052886814</v>
       </c>
       <c r="B30">
-        <v>-1.9951443685767527</v>
+        <v>-2.317156627009707</v>
       </c>
       <c r="C30">
         <v>194.11826296981104</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.4483198826152357</v>
+        <v>-7.3269749598570275</v>
       </c>
       <c r="B31">
-        <v>-2.4740107028964142</v>
+        <v>-2.8131185487703076</v>
       </c>
       <c r="C31">
         <v>194.11826296981104</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.8250145428570477</v>
+        <v>-7.6809446276346494</v>
       </c>
       <c r="B32">
-        <v>-2.960702187395686</v>
+        <v>-3.3165795129295943</v>
       </c>
       <c r="C32">
         <v>194.11826296981104</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.194896094080125</v>
+        <v>-8.0277553423414858</v>
       </c>
       <c r="B33">
-        <v>-3.4550884076269432</v>
+        <v>-3.8274145399728385</v>
       </c>
       <c r="C33">
         <v>194.11826296981104</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.5580148016005477</v>
+        <v>-8.367459920839547</v>
       </c>
       <c r="B34">
-        <v>-3.9571125938654363</v>
+        <v>-4.3455692260147352</v>
       </c>
       <c r="C34">
         <v>194.11826296981104</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.9141601033099924</v>
+        <v>-8.6998371125591127</v>
       </c>
       <c r="B35">
-        <v>-4.4670125552779076</v>
+        <v>-4.8712714696876773</v>
       </c>
       <c r="C35">
         <v>194.11826296981104</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-9.2630562302440413</v>
+        <v>-9.0245971500725357</v>
       </c>
       <c r="B36">
-        <v>-4.98509974575397</v>
+        <v>-5.4048197452534783</v>
       </c>
       <c r="C36">
         <v>194.11826296981104</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.6044274134382839</v>
+        <v>-9.3414502659521723</v>
       </c>
       <c r="B37">
-        <v>-5.5116856191832468</v>
+        <v>-5.9465125269739652</v>
       </c>
       <c r="C37">
         <v>194.11826296981104</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.9378430140245442</v>
+        <v>-9.64994396142848</v>
       </c>
       <c r="B38">
-        <v>-6.0472565397612055</v>
+        <v>-6.4968159101494543</v>
       </c>
       <c r="C38">
         <v>194.11826296981104</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-10.262252913519596</v>
+        <v>-9.9489748123643338</v>
       </c>
       <c r="B39">
-        <v>-6.5929985129067266</v>
+        <v>-7.0568664742342841</v>
       </c>
       <c r="C39">
         <v>194.11826296981104</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-10.576452123536464</v>
+        <v>-10.23727666328071</v>
       </c>
       <c r="B40">
-        <v>-7.1502724543445435</v>
+        <v>-7.6279684197213</v>
       </c>
       <c r="C40">
         <v>194.11826296981104</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-10.879235655688166</v>
+        <v>-10.513583358698593</v>
       </c>
       <c r="B41">
-        <v>-7.72043927979939</v>
+        <v>-8.2114259471033417</v>
       </c>
       <c r="C41">
         <v>194.11826296981104</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-10.879235655688166</v>
+        <v>-10.513583358698593</v>
       </c>
       <c r="B42">
-        <v>-7.72043927979939</v>
+        <v>-8.2114259471033417</v>
       </c>
       <c r="C42">
         <v>194.11826296981104</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-10.523674969235302</v>
+        <v>-10.181820458218873</v>
       </c>
       <c r="B43">
-        <v>-7.20987905302321</v>
+        <v>-7.6850909541740684</v>
       </c>
       <c r="C43">
         <v>194.11826296981104</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-10.165762663765948</v>
+        <v>-9.8475865668694755</v>
       </c>
       <c r="B44">
-        <v>-6.701974748356073</v>
+        <v>-7.16130119961673</v>
       </c>
       <c r="C44">
         <v>194.11826296981104</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-9.804469985600571</v>
+        <v>-9.5098007098277559</v>
       </c>
       <c r="B45">
-        <v>-6.1978882417749457</v>
+        <v>-6.6411701390217459</v>
       </c>
       <c r="C45">
         <v>194.11826296981104</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-9.438768181059638</v>
+        <v>-9.1673819122710718</v>
       </c>
       <c r="B46">
-        <v>-5.6987814092568</v>
+        <v>-6.1258112279795229</v>
       </c>
       <c r="C46">
         <v>194.11826296981104</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-9.0677757899135472</v>
+        <v>-8.8194039696722175</v>
       </c>
       <c r="B47">
-        <v>-5.20564977333127</v>
+        <v>-5.6161785012992667</v>
       </c>
       <c r="C47">
         <v>194.11826296981104</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.6912005257324356</v>
+        <v>-8.4655597586857674</v>
       </c>
       <c r="B48">
-        <v>-4.7188234427386835</v>
+        <v>-5.1125883106653616</v>
       </c>
       <c r="C48">
         <v>194.11826296981104</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-8.3088973955363752</v>
+        <v>-8.1056969262617287</v>
       </c>
       <c r="B49">
-        <v>-4.2384661727720241</v>
+        <v>-4.6151975869809752</v>
       </c>
       <c r="C49">
         <v>194.11826296981104</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.9207214063454332</v>
+        <v>-7.7396631193501158</v>
       </c>
       <c r="B50">
-        <v>-3.7647417187242871</v>
+        <v>-4.1241632611492829</v>
       </c>
       <c r="C50">
         <v>194.11826296981104</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.5265855264922035</v>
+        <v>-7.3673668884201877</v>
       </c>
       <c r="B51">
-        <v>-3.2977483742935734</v>
+        <v>-3.6395795305457557</v>
       </c>
       <c r="C51">
         <v>194.11826296981104</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.1266345695593705</v>
+        <v>-6.9889603980182011</v>
       </c>
       <c r="B52">
-        <v>-2.8373225867984138</v>
+        <v>-3.1612896584350483</v>
       </c>
       <c r="C52">
         <v>194.11826296981104</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.7210713104421389</v>
+        <v>-6.6046567162096634</v>
       </c>
       <c r="B53">
-        <v>-2.3832353419624512</v>
+        <v>-2.6890741745541087</v>
       </c>
       <c r="C53">
         <v>194.11826296981104</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.3100985240357117</v>
+        <v>-6.2146689110600812</v>
       </c>
       <c r="B54">
-        <v>-1.9352576255093246</v>
+        <v>-2.2227136086398889</v>
       </c>
       <c r="C54">
         <v>194.11826296981104</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.8938777654190346</v>
+        <v>-5.8191667384364631</v>
       </c>
       <c r="B55">
-        <v>-1.4932069768861198</v>
+        <v>-1.7620331040582031</v>
       </c>
       <c r="C55">
         <v>194.11826296981104</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.4724057104059982</v>
+        <v>-5.4181467054118251</v>
       </c>
       <c r="B56">
-        <v>-1.0570871504337032</v>
+        <v>-1.3070362586903319</v>
       </c>
       <c r="C56">
         <v>194.11826296981104</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.0456378149942358</v>
+        <v>-5.0115620068606832</v>
       </c>
       <c r="B57">
-        <v>-0.6269484542163859</v>
+        <v>-0.85777128404641767</v>
       </c>
       <c r="C57">
         <v>194.11826296981104</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.61352953518138</v>
+        <v>-4.5993658376575608</v>
       </c>
       <c r="B58">
-        <v>-0.20284119629848141</v>
+        <v>-0.4142863916366088</v>
       </c>
       <c r="C58">
         <v>194.11826296981104</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.1760419091849084</v>
+        <v>-4.1815172582590163</v>
       </c>
       <c r="B59">
-        <v>0.21519061982333032</v>
+        <v>0.023376248858039943</v>
       </c>
       <c r="C59">
         <v>194.11826296981104</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-3.7331583041017118</v>
+        <v>-3.75799879144981</v>
       </c>
       <c r="B60">
-        <v>0.62712820892286836</v>
+        <v>0.45519863507279729</v>
       </c>
       <c r="C60">
         <v>194.11826296981104</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.2848676692485315</v>
+        <v>-3.3287988255967438</v>
       </c>
       <c r="B61">
-        <v>1.0329590903415811</v>
+        <v>0.88116880647202012</v>
       </c>
       <c r="C61">
         <v>194.11826296981104</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-2.8311589539421078</v>
+        <v>-2.8939057490666209</v>
       </c>
       <c r="B62">
-        <v>1.4326707834209158</v>
+        <v>1.3012748025200631</v>
       </c>
       <c r="C62">
         <v>194.11826296981104</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.3720694020081319</v>
+        <v>-2.4533586962398783</v>
       </c>
       <c r="B63">
-        <v>1.8263053513944909</v>
+        <v>1.7155569334940573</v>
       </c>
       <c r="C63">
         <v>194.11826296981104</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-1.9078294353080847</v>
+        <v>-2.0073997855514771</v>
       </c>
       <c r="B64">
-        <v>2.2141230330646122</v>
+        <v>2.124264592922239</v>
       </c>
       <c r="C64">
         <v>194.11826296981104</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.438717770212403</v>
+        <v>-1.5563218814500148</v>
       </c>
       <c r="B65">
-        <v>2.5964386111257509</v>
+        <v>2.5276994451456156</v>
       </c>
       <c r="C65">
         <v>194.11826296981104</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.96501312309151688</v>
+        <v>-1.1004178483840841</v>
       </c>
       <c r="B66">
-        <v>2.9735668682723837</v>
+        <v>2.9261631545051987</v>
       </c>
       <c r="C66">
         <v>194.11826296981104</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.48662057961516586</v>
+        <v>-0.63958795402381663</v>
       </c>
       <c r="B67">
-        <v>3.3454006081149412</v>
+        <v>3.3195529919476274</v>
       </c>
       <c r="C67">
         <v>194.11826296981104</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.0019507026503069909</v>
+        <v>-0.17216207892548746</v>
       </c>
       <c r="B68">
-        <v>3.7101447179276845</v>
+        <v>3.7061486548420559</v>
       </c>
       <c r="C68">
         <v>194.11826296981104</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.49023555064824736</v>
+        <v>0.30316171550560544</v>
       </c>
       <c r="B69">
-        <v>4.0663998208287664</v>
+        <v>4.08460908438094</v>
       </c>
       <c r="C69">
         <v>194.11826296981104</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.98828112317148054</v>
+        <v>0.78464225735419579</v>
       </c>
       <c r="B70">
-        <v>4.4160373996480677</v>
+        <v>4.45672777062742</v>
       </c>
       <c r="C70">
         <v>194.11826296981104</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1.4903795405624183</v>
+        <v>1.2703813728042483</v>
       </c>
       <c r="B71">
-        <v>4.76109768928354</v>
+        <v>4.8244599230857022</v>
       </c>
       <c r="C71">
         <v>194.11826296981104</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>1.9970227594264407</v>
+        <v>1.7608959909465936</v>
       </c>
       <c r="B72">
-        <v>5.1010250731936564</v>
+        <v>5.1872730801535551</v>
       </c>
       <c r="C72">
         <v>194.11826296981104</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2.5090109181531681</v>
+        <v>2.257026866444876</v>
       </c>
       <c r="B73">
-        <v>5.4349158738590635</v>
+        <v>5.5443012244540837</v>
       </c>
       <c r="C73">
         <v>194.11826296981104</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>3.0260784513068049</v>
+        <v>2.7584949533471157</v>
       </c>
       <c r="B74">
-        <v>5.7630700212885664</v>
+        <v>5.8958317866181424</v>
       </c>
       <c r="C74">
         <v>194.11826296981104</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>3.5476892356410064</v>
+        <v>3.2647369139538576</v>
       </c>
       <c r="B75">
-        <v>6.0860930138954572</v>
+        <v>6.2424450313268443</v>
       </c>
       <c r="C75">
         <v>194.11826296981104</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>4.0732906204926245</v>
+        <v>3.7751720441913643</v>
       </c>
       <c r="B76">
-        <v>6.4046090161828007</v>
+        <v>6.5847391114545459</v>
       </c>
       <c r="C76">
         <v>194.11826296981104</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>4.6023788424452388</v>
+        <v>4.2892710088255992</v>
       </c>
       <c r="B77">
-        <v>6.7191869793225436</v>
+        <v>6.9232592675222984</v>
       </c>
       <c r="C77">
         <v>194.11826296981104</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5.1346622144860943</v>
+        <v>4.8067273143555891</v>
       </c>
       <c r="B78">
-        <v>7.0301563350724079</v>
+        <v>7.2583212024446722</v>
       </c>
       <c r="C78">
         <v>194.11826296981104</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>5.6695989847389</v>
+        <v>5.326971708733887</v>
       </c>
       <c r="B79">
-        <v>7.3381289388289419</v>
+        <v>7.5905112729630995</v>
       </c>
       <c r="C79">
         <v>194.11826296981104</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6.2061919978355835</v>
+        <v>5.8489564194289434</v>
       </c>
       <c r="B80">
-        <v>7.6442309793878831</v>
+        <v>7.9209087347256322</v>
       </c>
       <c r="C80">
         <v>194.11826296981104</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>6.74188265288036</v>
+        <v>6.3699929669684</v>
       </c>
       <c r="B81">
-        <v>7.9513521445088911</v>
+        <v>8.25228284973124</v>
       </c>
       <c r="C81">
         <v>194.11826296981104</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7.2291451102383748</v>
+        <v>6.8401430258888</v>
       </c>
       <c r="B82">
-        <v>8.3131681900657419</v>
+        <v>8.6360724734446919</v>
       </c>
       <c r="C82">
         <v>194.11826296981104</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>7.5772319335061669</v>
+        <v>7.1335675507198451</v>
       </c>
       <c r="B1">
-        <v>9.53124713634847</v>
+        <v>9.8676912065393161</v>
       </c>
       <c r="C1">
         <v>215.66601106843655</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>6.7780573466510505</v>
+        <v>6.3054379943336141</v>
       </c>
       <c r="B2">
-        <v>9.3986808397454364</v>
+        <v>9.7327622858672669</v>
       </c>
       <c r="C2">
         <v>215.66601106843655</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>6.0935486661956428</v>
+        <v>5.6195937443953419</v>
       </c>
       <c r="B3">
-        <v>9.1468277443951287</v>
+        <v>9.462756736744188</v>
       </c>
       <c r="C3">
         <v>215.66601106843655</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>5.4319261232061748</v>
+        <v>4.9608007946342294</v>
       </c>
       <c r="B4">
-        <v>8.8711662289161222</v>
+        <v>9.1670704022022473</v>
       </c>
       <c r="C4">
         <v>215.66601106843655</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>4.7879889001695464</v>
+        <v>4.3225505726512923</v>
       </c>
       <c r="B5">
-        <v>8.5771066972504872</v>
+        <v>8.8518821072911358</v>
       </c>
       <c r="C5">
         <v>215.66601106843655</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4.1595618687841043</v>
+        <v>3.7021325506062235</v>
       </c>
       <c r="B6">
-        <v>8.2669119326449341</v>
+        <v>8.51976505490251</v>
       </c>
       <c r="C6">
         <v>215.66601106843655</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>3.5453710805048551</v>
+        <v>3.0979658817517075</v>
       </c>
       <c r="B7">
-        <v>7.9419072221745077</v>
+        <v>8.17222000048368</v>
       </c>
       <c r="C7">
         <v>215.66601106843655</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2.9446357269201116</v>
+        <v>2.5090880376039282</v>
       </c>
       <c r="B8">
-        <v>7.6029048398515124</v>
+        <v>7.8101607074135124</v>
       </c>
       <c r="C8">
         <v>215.66601106843655</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.3561920020463827</v>
+        <v>1.9340534311039475</v>
       </c>
       <c r="B9">
-        <v>7.2511154915822829</v>
+        <v>7.4349595241862252</v>
       </c>
       <c r="C9">
         <v>215.66601106843655</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>1.778793839571561</v>
+        <v>1.3713121941736355</v>
       </c>
       <c r="B10">
-        <v>6.8878354585899428</v>
+        <v>7.04808779706915</v>
       </c>
       <c r="C10">
         <v>215.66601106843655</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.2112491294408554</v>
+        <v>0.81938039323319833</v>
       </c>
       <c r="B11">
-        <v>6.5143048914707338</v>
+        <v>6.6509542783066822</v>
       </c>
       <c r="C11">
         <v>215.66601106843655</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.652897201590153</v>
+        <v>0.277440609181466</v>
       </c>
       <c r="B12">
-        <v>6.1312110844645078</v>
+        <v>6.2443349736507443</v>
       </c>
       <c r="C12">
         <v>215.66601106843655</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.1051491896607499</v>
+        <v>-0.25272445366657886</v>
       </c>
       <c r="B13">
-        <v>5.7370860370124284</v>
+        <v>5.8265374969062744</v>
       </c>
       <c r="C13">
         <v>215.66601106843655</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.43116668543383313</v>
+        <v>-0.77006496901021626</v>
       </c>
       <c r="B14">
-        <v>5.3310681519359493</v>
+        <v>5.3965652096943666</v>
       </c>
       <c r="C14">
         <v>215.66601106843655</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.959625657396595</v>
+        <v>-1.2790627460219373</v>
       </c>
       <c r="B15">
-        <v>4.9168767403764049</v>
+        <v>4.958672856847735</v>
       </c>
       <c r="C15">
         <v>215.66601106843655</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.4835066970490425</v>
+        <v>-1.7838282521944042</v>
       </c>
       <c r="B16">
-        <v>4.4979229115707495</v>
+        <v>4.5167626550051008</v>
       </c>
       <c r="C16">
         <v>215.66601106843655</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.0005002690702338</v>
+        <v>-2.2814549528277781</v>
       </c>
       <c r="B17">
-        <v>4.07180405881853</v>
+        <v>4.0680753248175865</v>
       </c>
       <c r="C17">
         <v>215.66601106843655</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.507611513113003</v>
+        <v>-2.7681765604783735</v>
       </c>
       <c r="B18">
-        <v>3.6354046326532581</v>
+        <v>3.6090353923141261</v>
       </c>
       <c r="C18">
         <v>215.66601106843655</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.0046927748677654</v>
+        <v>-3.2438047789196469</v>
       </c>
       <c r="B19">
-        <v>3.1885710284816864</v>
+        <v>3.1394641010224804</v>
       </c>
       <c r="C19">
         <v>215.66601106843655</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.4923082015343283</v>
+        <v>-3.7090458097293384</v>
       </c>
       <c r="B20">
-        <v>2.7318901279288768</v>
+        <v>2.6600318738451207</v>
       </c>
       <c r="C20">
         <v>215.66601106843655</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.971021940312498</v>
+        <v>-4.1646058544851856</v>
       </c>
       <c r="B21">
-        <v>2.2659488126198966</v>
+        <v>2.1714091336845192</v>
       </c>
       <c r="C21">
         <v>215.66601106843655</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.4412961425880138</v>
+        <v>-4.6110637663829381</v>
       </c>
       <c r="B22">
-        <v>1.7912278580622314</v>
+        <v>1.6741454069816097</v>
       </c>
       <c r="C22">
         <v>215.66601106843655</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.903184976490329</v>
+        <v>-5.0484890050903779</v>
       </c>
       <c r="B23">
-        <v>1.3077836152930837</v>
+        <v>1.1683066343311845</v>
       </c>
       <c r="C23">
         <v>215.66601106843655</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.3566406143348306</v>
+        <v>-5.4768236818932889</v>
       </c>
       <c r="B24">
-        <v>0.81556632923207883</v>
+        <v>0.65383785986649878</v>
       </c>
       <c r="C24">
         <v>215.66601106843655</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.8016152284369049</v>
+        <v>-5.8960099080774633</v>
       </c>
       <c r="B25">
-        <v>0.31452624479884123</v>
+        <v>0.1306841277208034</v>
       </c>
       <c r="C25">
         <v>215.66601106843655</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.2380413249129241</v>
+        <v>-6.3059658287095059</v>
       </c>
       <c r="B26">
-        <v>-0.19540685180919043</v>
+        <v>-0.40123226997820521</v>
       </c>
       <c r="C26">
         <v>215.66601106843655</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.66577274508322</v>
+        <v>-6.7065137239792971</v>
       </c>
       <c r="B27">
-        <v>-0.71438500928334114</v>
+        <v>-0.94208004912509469</v>
       </c>
       <c r="C27">
         <v>215.66601106843655</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.0846436640691079</v>
+        <v>-7.0974519078575282</v>
       </c>
       <c r="B28">
-        <v>-1.2425807350371185</v>
+        <v>-1.4920506776199878</v>
       </c>
       <c r="C28">
         <v>215.66601106843655</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.4944882569919047</v>
+        <v>-7.478578694314896</v>
       </c>
       <c r="B29">
-        <v>-1.7801665364840313</v>
+        <v>-2.0513356233630096</v>
       </c>
       <c r="C29">
         <v>215.66601106843655</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.8952103663177953</v>
+        <v>-7.8497806811860125</v>
       </c>
       <c r="B30">
-        <v>-2.3272424461860197</v>
+        <v>-2.6200425431638594</v>
       </c>
       <c r="C30">
         <v>215.66601106843655</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.2869925038924421</v>
+        <v>-8.21129760176118</v>
       </c>
       <c r="B31">
-        <v>-2.8836185972987289</v>
+        <v>-3.1979438494705232</v>
       </c>
       <c r="C31">
         <v>215.66601106843655</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.6700868489063776</v>
+        <v>-8.5634574731946227</v>
       </c>
       <c r="B32">
-        <v>-3.4490326481262459</v>
+        <v>-3.7847281436405749</v>
       </c>
       <c r="C32">
         <v>215.66601106843655</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-9.0447455805501349</v>
+        <v>-8.90658831264056</v>
       </c>
       <c r="B33">
-        <v>-4.0232222569726446</v>
+        <v>-4.3800840270315762</v>
       </c>
       <c r="C33">
         <v>215.66601106843655</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-9.4110978054497263</v>
+        <v>-9.2408645289374132</v>
       </c>
       <c r="B34">
-        <v>-4.6060531143766559</v>
+        <v>-4.9838459269750963</v>
       </c>
       <c r="C34">
         <v>215.66601106843655</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-9.7687803399730928</v>
+        <v>-9.5658460976604065</v>
       </c>
       <c r="B35">
-        <v>-5.19790303981564</v>
+        <v>-5.596431574698765</v>
       </c>
       <c r="C35">
         <v>215.66601106843655</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-10.117306927923647</v>
+        <v>-9.8809393860689667</v>
       </c>
       <c r="B36">
-        <v>-5.7992778850015965</v>
+        <v>-6.2184045274042052</v>
       </c>
       <c r="C36">
         <v>215.66601106843655</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-10.456191313104814</v>
+        <v>-10.185550761422524</v>
       </c>
       <c r="B37">
-        <v>-6.4106835016465391</v>
+        <v>-6.8503283422930537</v>
       </c>
       <c r="C37">
         <v>215.66601106843655</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-10.78465165316854</v>
+        <v>-10.478716387760594</v>
       </c>
       <c r="B38">
-        <v>-7.0329332393654687</v>
+        <v>-7.4931180239794264</v>
       </c>
       <c r="C38">
         <v>215.66601106843655</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-11.100723761160904</v>
+        <v>-10.757991616243094</v>
       </c>
       <c r="B39">
-        <v>-7.6680704393853514</v>
+        <v>-8.1490943667273878</v>
       </c>
       <c r="C39">
         <v>215.66601106843655</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-11.402147863976513</v>
+        <v>-11.020561594810042</v>
       </c>
       <c r="B40">
-        <v>-8.3184459408361562</v>
+        <v>-8.82092961221349</v>
       </c>
       <c r="C40">
         <v>215.66601106843655</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-11.686664188509978</v>
+        <v>-11.263611471401442</v>
       </c>
       <c r="B41">
-        <v>-8.986410582847844</v>
+        <v>-9.5112960021142872</v>
       </c>
       <c r="C41">
         <v>215.66601106843655</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-11.686664188509978</v>
+        <v>-11.263611471401442</v>
       </c>
       <c r="B42">
-        <v>-8.986410582847844</v>
+        <v>-9.5112960021142872</v>
       </c>
       <c r="C42">
         <v>215.66601106843655</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-11.300558199831064</v>
+        <v>-10.892983593410962</v>
       </c>
       <c r="B43">
-        <v>-8.4241295411513146</v>
+        <v>-8.9420440598237985</v>
       </c>
       <c r="C43">
         <v>215.66601106843655</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-10.914991654237365</v>
+        <v>-10.524746126199739</v>
       </c>
       <c r="B44">
-        <v>-7.8612873174891718</v>
+        <v>-8.3705228134376384</v>
       </c>
       <c r="C44">
         <v>215.66601106843655</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-10.527924640447539</v>
+        <v>-10.156314306174735</v>
       </c>
       <c r="B45">
-        <v>-7.3000060290113211</v>
+        <v>-7.7991860732627742</v>
       </c>
       <c r="C45">
         <v>215.66601106843655</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-10.137317247180253</v>
+        <v>-9.785103369742906</v>
       </c>
       <c r="B46">
-        <v>-6.7424077928676578</v>
+        <v>-7.2304876496061672</v>
       </c>
       <c r="C46">
         <v>215.66601106843655</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-9.7414156050579628</v>
+        <v>-9.4088887683427362</v>
       </c>
       <c r="B47">
-        <v>-6.1903171571739763</v>
+        <v>-6.6665393875136365</v>
       </c>
       <c r="C47">
         <v>215.66601106843655</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-9.3396100123183476</v>
+        <v>-9.0268868135388569</v>
       </c>
       <c r="B48">
-        <v>-5.6443683939096463</v>
+        <v>-6.108085270986404</v>
       </c>
       <c r="C48">
         <v>215.66601106843655</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-8.93157680910288</v>
+        <v>-8.638674031927426</v>
       </c>
       <c r="B49">
-        <v>-5.104898206019933</v>
+        <v>-5.5555273187645389</v>
       </c>
       <c r="C49">
         <v>215.66601106843655</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-8.5169923355530415</v>
+        <v>-8.2438269501046069</v>
       </c>
       <c r="B50">
-        <v>-4.5722432964501039</v>
+        <v>-5.0092675495881238</v>
       </c>
       <c r="C50">
         <v>215.66601106843655</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-8.095646943132726</v>
+        <v>-7.8420662202660587</v>
       </c>
       <c r="B51">
-        <v>-4.0466217623095613</v>
+        <v>-4.4695711585114868</v>
       </c>
       <c r="C51">
         <v>215.66601106843655</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.6677870285955452</v>
+        <v>-7.4336889970054632</v>
       </c>
       <c r="B52">
-        <v>-3.5277772773642733</v>
+        <v>-3.936156045846023</v>
       </c>
       <c r="C52">
         <v>215.66601106843655</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-7.23377300001753</v>
+        <v>-7.0191365605160039</v>
       </c>
       <c r="B53">
-        <v>-3.0153349095443533</v>
+        <v>-3.408603288217388</v>
       </c>
       <c r="C53">
         <v>215.66601106843655</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.793965265474708</v>
+        <v>-6.5988501909908566</v>
       </c>
       <c r="B54">
-        <v>-2.5089197267799026</v>
+        <v>-2.8864939622512278</v>
       </c>
       <c r="C54">
         <v>215.66601106843655</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.3486469743458347</v>
+        <v>-6.1731749403030562</v>
       </c>
       <c r="B55">
-        <v>-2.0082371691270033</v>
+        <v>-2.3695004976255407</v>
       </c>
       <c r="C55">
         <v>215.66601106843655</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.897792241220551</v>
+        <v>-5.7420709470450273</v>
       </c>
       <c r="B56">
-        <v>-1.5133141651456172</v>
+        <v>-1.857660736227694</v>
       </c>
       <c r="C56">
         <v>215.66601106843655</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.44129792199122</v>
+        <v>-5.3054021214890472</v>
       </c>
       <c r="B57">
-        <v>-1.0242580155216765</v>
+        <v>-1.351103872997393</v>
       </c>
       <c r="C57">
         <v>215.66601106843655</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.9790608725502041</v>
+        <v>-4.8630323739073926</v>
       </c>
       <c r="B58">
-        <v>-0.541176020941116</v>
+        <v>-0.84995910287434917</v>
       </c>
       <c r="C58">
         <v>215.66601106843655</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.5109906306304488</v>
+        <v>-4.41484227156296</v>
       </c>
       <c r="B59">
-        <v>-0.064162289186993349</v>
+        <v>-0.35433980770983042</v>
       </c>
       <c r="C59">
         <v>215.66601106843655</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.0370474613272407</v>
+        <v>-3.9607790096811537</v>
       </c>
       <c r="B60">
-        <v>0.4067418435691017</v>
+        <v>0.13570388299862368</v>
       </c>
       <c r="C60">
         <v>215.66601106843655</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.5572043115764478</v>
+        <v>-3.5008064404779966</v>
       </c>
       <c r="B61">
-        <v>0.87150823405845623</v>
+        <v>0.6201376528419138</v>
       </c>
       <c r="C61">
         <v>215.66601106843655</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.0714341283139408</v>
+        <v>-3.0348884161695158</v>
       </c>
       <c r="B62">
-        <v>1.3301087390123518</v>
+        <v>1.098927185410937</v>
       </c>
       <c r="C62">
         <v>215.66601106843655</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.5798047863544387</v>
+        <v>-2.5631087406608892</v>
       </c>
       <c r="B63">
-        <v>1.7826139685154889</v>
+        <v>1.5721520388079646</v>
       </c>
       <c r="C63">
         <v>215.66601106843655</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.082763872028047</v>
+        <v>-2.0860310246138982</v>
       </c>
       <c r="B64">
-        <v>2.2294895460662394</v>
+        <v>2.0403472691807729</v>
       </c>
       <c r="C64">
         <v>215.66601106843655</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.5808538995437218</v>
+        <v>-1.6043388303794781</v>
       </c>
       <c r="B65">
-        <v>2.6712998485163877</v>
+        <v>2.5041618071885052</v>
       </c>
       <c r="C65">
         <v>215.66601106843655</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.0746173831104182</v>
+        <v>-1.1187157203085623</v>
       </c>
       <c r="B66">
-        <v>3.1086092527177227</v>
+        <v>2.96424458349031</v>
       </c>
       <c r="C66">
         <v>215.66601106843655</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.56387924908013565</v>
+        <v>-0.62894470345433184</v>
       </c>
       <c r="B67">
-        <v>3.5412356297736052</v>
+        <v>3.4203896006699264</v>
       </c>
       <c r="C67">
         <v>215.66601106843655</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.045594072377065212</v>
+        <v>-0.13120657567896699</v>
       </c>
       <c r="B68">
-        <v>3.9660108277936876</v>
+        <v>3.8689711490094467</v>
       </c>
       <c r="C68">
         <v>215.66601106843655</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.48260675051994351</v>
+        <v>0.37746701341315714</v>
       </c>
       <c r="B69">
-        <v>4.3804707915028658</v>
+        <v>4.30717126526649</v>
       </c>
       <c r="C69">
         <v>215.66601106843655</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.017514185485553</v>
+        <v>0.89303878605785714</v>
       </c>
       <c r="B70">
-        <v>4.7879538750806931</v>
+        <v>4.7388226844023755</v>
       </c>
       <c r="C70">
         <v>215.66601106843655</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1.5556297219279638</v>
+        <v>1.4111072248891456</v>
       </c>
       <c r="B71">
-        <v>5.1920995747120662</v>
+        <v>5.1681039273108569</v>
       </c>
       <c r="C71">
         <v>215.66601106843655</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2.0978745810359749</v>
+        <v>1.9328194822936002</v>
       </c>
       <c r="B72">
-        <v>5.5919495451486005</v>
+        <v>5.5939259604116813</v>
       </c>
       <c r="C72">
         <v>215.66601106843655</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2.6457609850041872</v>
+        <v>2.4600640531678821</v>
       </c>
       <c r="B73">
-        <v>5.9859306235361167</v>
+        <v>6.0144959666539775</v>
       </c>
       <c r="C73">
         <v>215.66601106843655</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>3.1987454282698149</v>
+        <v>2.9921461326964338</v>
       </c>
       <c r="B74">
-        <v>6.3746082180305486</v>
+        <v>6.4304735495784033</v>
       </c>
       <c r="C74">
         <v>215.66601106843655</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>3.7557613431980559</v>
+        <v>3.5277131691938708</v>
       </c>
       <c r="B75">
-        <v>6.75909187760594</v>
+        <v>6.8431427358074508</v>
       </c>
       <c r="C75">
         <v>215.66601106843655</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>4.3157056416234223</v>
+        <v>4.0653649232076949</v>
       </c>
       <c r="B76">
-        <v>7.140529143498636</v>
+        <v>7.2538328236993852</v>
       </c>
       <c r="C76">
         <v>215.66601106843655</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>4.8775668326225468</v>
+        <v>4.6038152075148773</v>
       </c>
       <c r="B77">
-        <v>7.5199722684487842</v>
+        <v>7.6637648376732521</v>
       </c>
       <c r="C77">
         <v>215.66601106843655</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5.4407363347712172</v>
+        <v>5.14228173157734</v>
       </c>
       <c r="B78">
-        <v>7.8980543589494188</v>
+        <v>8.0736814346554056</v>
       </c>
       <c r="C78">
         <v>215.66601106843655</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6.0041217467293411</v>
+        <v>5.6793736403311046</v>
       </c>
       <c r="B79">
-        <v>8.2759118387458237</v>
+        <v>8.4849030040619891</v>
       </c>
       <c r="C79">
         <v>215.66601106843655</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6.5657489380351484</v>
+        <v>6.2125907529801419</v>
       </c>
       <c r="B80">
-        <v>8.6555983932837162</v>
+        <v>8.8998030586672776</v>
       </c>
       <c r="C80">
         <v>215.66601106843655</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7.1206340144561819</v>
+        <v>6.7356515103657237</v>
       </c>
       <c r="B81">
-        <v>9.0422987614881372</v>
+        <v>9.3243449115761745</v>
       </c>
       <c r="C81">
         <v>215.66601106843655</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7.5772319335061669</v>
+        <v>7.1335675507198451</v>
       </c>
       <c r="B82">
-        <v>9.53124713634847</v>
+        <v>9.8676912065393161</v>
       </c>
       <c r="C82">
         <v>215.66601106843655</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>7.8593447057755306</v>
+        <v>7.3622491622336863</v>
       </c>
       <c r="B1">
-        <v>10.641293967746487</v>
+        <v>10.991093460469035</v>
       </c>
       <c r="C1">
         <v>235.24828722421182</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>6.917208934980839</v>
+        <v>6.3451700881254709</v>
       </c>
       <c r="B2">
-        <v>10.545414362097858</v>
+        <v>10.923303480157015</v>
       </c>
       <c r="C2">
         <v>235.24828722421182</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>6.1519251278883029</v>
+        <v>5.5625973586881807</v>
       </c>
       <c r="B3">
-        <v>10.277533537518886</v>
+        <v>10.647520831163337</v>
       </c>
       <c r="C3">
         <v>235.24828722421182</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>5.4191672637114419</v>
+        <v>4.8209174744008916</v>
       </c>
       <c r="B4">
-        <v>9.9780189006189133</v>
+        <v>10.335468749866367</v>
       </c>
       <c r="C4">
         <v>235.24828722421182</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>4.7107973773275074</v>
+        <v>4.1092490499098666</v>
       </c>
       <c r="B5">
-        <v>9.6547852061534041</v>
+        <v>9.99679835415741</v>
       </c>
       <c r="C5">
         <v>235.24828722421182</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>4.0234339193232929</v>
+        <v>3.4230899801385974</v>
       </c>
       <c r="B6">
-        <v>9.3111212534592145</v>
+        <v>9.6355027336514212</v>
       </c>
       <c r="C6">
         <v>235.24828722421182</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>3.3551091305454457</v>
+        <v>2.7598317343077539</v>
       </c>
       <c r="B7">
-        <v>8.94894082944519</v>
+        <v>9.2538954943145555</v>
       </c>
       <c r="C7">
         <v>235.24828722421182</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2.7046291514785645</v>
+        <v>2.1179025481765956</v>
       </c>
       <c r="B8">
-        <v>8.5694050481164155</v>
+        <v>8.85337069411752</v>
       </c>
       <c r="C8">
         <v>235.24828722421182</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.0701937431560307</v>
+        <v>1.4949135225685442</v>
       </c>
       <c r="B9">
-        <v>8.1742647709852143</v>
+        <v>8.4360471393367344</v>
       </c>
       <c r="C9">
         <v>235.24828722421182</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>1.4498714276527507</v>
+        <v>0.88829802286702431</v>
       </c>
       <c r="B10">
-        <v>7.7653984988637781</v>
+        <v>8.00420127662519</v>
       </c>
       <c r="C10">
         <v>235.24828722421182</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.84181215066093118</v>
+        <v>0.29559560763129905</v>
       </c>
       <c r="B11">
-        <v>7.344605542256593</v>
+        <v>7.5600153658365041</v>
       </c>
       <c r="C11">
         <v>235.24828722421182</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.24500016766025634</v>
+        <v>-0.28453616821614908</v>
       </c>
       <c r="B12">
-        <v>6.9128737855611977</v>
+        <v>7.1046800729828155</v>
       </c>
       <c r="C12">
         <v>235.24828722421182</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.33832445033698744</v>
+        <v>-0.84907395747578673</v>
       </c>
       <c r="B13">
-        <v>6.4680245990550995</v>
+        <v>6.6355138755097425</v>
       </c>
       <c r="C13">
         <v>235.24828722421182</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.90684018696689372</v>
+        <v>-1.3962283325567306</v>
       </c>
       <c r="B14">
-        <v>6.0087727132921991</v>
+        <v>6.150929661475546</v>
       </c>
       <c r="C14">
         <v>235.24828722421182</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.46615555999167</v>
+        <v>-1.9335113365797183</v>
       </c>
       <c r="B15">
-        <v>5.5405728140520516</v>
+        <v>5.6575901499555918</v>
       </c>
       <c r="C15">
         <v>235.24828722421182</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.0214144151110691</v>
+        <v>-2.4678127083816528</v>
       </c>
       <c r="B16">
-        <v>5.0684276602061207</v>
+        <v>5.1616061144951271</v>
       </c>
       <c r="C16">
         <v>235.24828722421182</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.5689718756489084</v>
+        <v>-2.9942314989524754</v>
       </c>
       <c r="B17">
-        <v>4.5887923477678711</v>
+        <v>4.65863071550179</v>
       </c>
       <c r="C17">
         <v>235.24828722421182</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.1041067368281738</v>
+        <v>-3.5064240412501406</v>
       </c>
       <c r="B18">
-        <v>4.0970751664759852</v>
+        <v>4.143037511443036</v>
       </c>
       <c r="C18">
         <v>235.24828722421182</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.6265812038444896</v>
+        <v>-4.0040664839516094</v>
       </c>
       <c r="B19">
-        <v>3.593044843828014</v>
+        <v>3.6145392661631437</v>
       </c>
       <c r="C19">
         <v>235.24828722421182</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.1372783343866315</v>
+        <v>-4.4883399296635975</v>
       </c>
       <c r="B20">
-        <v>3.0775602167612224</v>
+        <v>3.0741835448506043</v>
       </c>
       <c r="C20">
         <v>235.24828722421182</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.6370811861433783</v>
+        <v>-4.9604254809928232</v>
       </c>
       <c r="B21">
-        <v>2.5514801222128778</v>
+        <v>2.5230179126939096</v>
       </c>
       <c r="C21">
         <v>235.24828722421182</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.1267138000790622</v>
+        <v>-5.4212921064589992</v>
       </c>
       <c r="B22">
-        <v>2.0155087419506761</v>
+        <v>1.9619017850260092</v>
       </c>
       <c r="C22">
         <v>235.24828722421182</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.606264150260226</v>
+        <v>-5.8710602382338584</v>
       </c>
       <c r="B23">
-        <v>1.4697316370640354</v>
+        <v>1.3909419777576992</v>
       </c>
       <c r="C23">
         <v>235.24828722421182</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.075661194028962</v>
+        <v>-6.3096381744021288</v>
       </c>
       <c r="B24">
-        <v>0.91407971347280248</v>
+        <v>0.81005715694423652</v>
       </c>
       <c r="C24">
         <v>235.24828722421182</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.5348338887273734</v>
+        <v>-6.7369342130485457</v>
       </c>
       <c r="B25">
-        <v>0.34848387709682022</v>
+        <v>0.21916598864087175</v>
       </c>
       <c r="C25">
         <v>235.24828722421182</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.9836816621694755</v>
+        <v>-7.1528182486633209</v>
       </c>
       <c r="B26">
-        <v>-0.22715368572804109</v>
+        <v>-0.38184692271760839</v>
       </c>
       <c r="C26">
         <v>235.24828722421182</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-7.4219858240569865</v>
+        <v>-7.5570065613585964</v>
       </c>
       <c r="B27">
-        <v>-0.81304566700184278</v>
+        <v>-0.99323321917832352</v>
       </c>
       <c r="C27">
         <v>235.24828722421182</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.8494981545635376</v>
+        <v>-7.9491770276519915</v>
       </c>
       <c r="B28">
-        <v>-1.4094334783086187</v>
+        <v>-1.6152786044088596</v>
       </c>
       <c r="C28">
         <v>235.24828722421182</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-8.265970433862762</v>
+        <v>-8.3290075240611241</v>
       </c>
       <c r="B29">
-        <v>-2.0165585312324046</v>
+        <v>-2.2482687820768024</v>
       </c>
       <c r="C29">
         <v>235.24828722421182</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-8.6712655499368729</v>
+        <v>-8.6963263374811639</v>
       </c>
       <c r="B30">
-        <v>-2.6345541770444987</v>
+        <v>-2.8923560511187651</v>
       </c>
       <c r="C30">
         <v>235.24828722421182</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-9.0656908220023436</v>
+        <v>-9.0515633963174675</v>
       </c>
       <c r="B31">
-        <v>-3.2631215257652273</v>
+        <v>-3.5471590915474409</v>
       </c>
       <c r="C31">
         <v>235.24828722421182</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.44966467708423</v>
+        <v>-9.3952990393529436</v>
       </c>
       <c r="B32">
-        <v>-3.9018536271021835</v>
+        <v>-4.2121631786445537</v>
       </c>
       <c r="C32">
         <v>235.24828722421182</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-9.82360554220758</v>
+        <v>-9.7281136053704937</v>
       </c>
       <c r="B33">
-        <v>-4.5503435307629543</v>
+        <v>-4.8868535876918218</v>
       </c>
       <c r="C33">
         <v>235.24828722421182</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-10.187740039245163</v>
+        <v>-10.05033166234546</v>
       </c>
       <c r="B34">
-        <v>-5.2083708307224255</v>
+        <v>-5.5709424469071118</v>
       </c>
       <c r="C34">
         <v>235.24828722421182</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-10.541527569460648</v>
+        <v>-10.361254695022963</v>
       </c>
       <c r="B35">
-        <v>-5.8764612980246769</v>
+        <v>-6.26504929625291</v>
       </c>
       <c r="C35">
         <v>235.24828722421182</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-10.884235728965404</v>
+        <v>-10.659928417340549</v>
       </c>
       <c r="B36">
-        <v>-6.5553272479810776</v>
+        <v>-6.970020528627848</v>
       </c>
       <c r="C36">
         <v>235.24828722421182</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-11.215132113870819</v>
+        <v>-10.94539854323577</v>
       </c>
       <c r="B37">
-        <v>-7.24568099590301</v>
+        <v>-7.6867025369305617</v>
       </c>
       <c r="C37">
         <v>235.24828722421182</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-11.53302121636966</v>
+        <v>-11.216091083072664</v>
       </c>
       <c r="B38">
-        <v>-7.9486852588775765</v>
+        <v>-8.4164913529201151</v>
       </c>
       <c r="C38">
         <v>235.24828722421182</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-11.834855112980231</v>
+        <v>-11.46795323292117</v>
       </c>
       <c r="B39">
-        <v>-8.66730436109481</v>
+        <v>-9.1629815637972829</v>
       </c>
       <c r="C39">
         <v>235.24828722421182</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-12.11712277630223</v>
+        <v>-11.69631248527771</v>
       </c>
       <c r="B40">
-        <v>-9.4049530285204845</v>
+        <v>-9.93031739562328</v>
       </c>
       <c r="C40">
         <v>235.24828722421182</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-12.376313178935344</v>
+        <v>-11.896496332638712</v>
       </c>
       <c r="B41">
-        <v>-10.165045987120355</v>
+        <v>-10.72264307445931</v>
       </c>
       <c r="C41">
         <v>235.24828722421182</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-12.376313178935344</v>
+        <v>-11.896496332638712</v>
       </c>
       <c r="B42">
-        <v>-10.165045987120355</v>
+        <v>-10.72264307445931</v>
       </c>
       <c r="C42">
         <v>235.24828722421182</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-11.957318941053254</v>
+        <v>-11.481889893410116</v>
       </c>
       <c r="B43">
-        <v>-9.5603737197990828</v>
+        <v>-10.120497013879504</v>
       </c>
       <c r="C43">
         <v>235.24828722421182</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-11.542692487333991</v>
+        <v>-11.075933433519573</v>
       </c>
       <c r="B44">
-        <v>-8.9514534691119216</v>
+        <v>-9.5106789549617083</v>
       </c>
       <c r="C44">
         <v>235.24828722421182</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-11.129181302241292</v>
+        <v>-10.674224231428708</v>
       </c>
       <c r="B45">
-        <v>-8.3414485396957936</v>
+        <v>-8.8970938402502942</v>
       </c>
       <c r="C45">
         <v>235.24828722421182</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-10.71353287023889</v>
+        <v>-10.272359565599134</v>
       </c>
       <c r="B46">
-        <v>-7.7335222361876195</v>
+        <v>-8.283646612289628</v>
       </c>
       <c r="C46">
         <v>235.24828722421182</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-10.292946491659292</v>
+        <v>-9.8665446377268857</v>
       </c>
       <c r="B47">
-        <v>-7.1303984398866644</v>
+        <v>-7.6737030231980921</v>
       </c>
       <c r="C47">
         <v>235.24828722421182</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-9.8664287303100959</v>
+        <v>-9.455416342445659</v>
       </c>
       <c r="B48">
-        <v>-6.5330433387415736</v>
+        <v>-7.0684720633901339</v>
       </c>
       <c r="C48">
         <v>235.24828722421182</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-9.4334379658676717</v>
+        <v>-9.038219497623551</v>
       </c>
       <c r="B49">
-        <v>-5.9419836973633284</v>
+        <v>-6.4686235328542088</v>
       </c>
       <c r="C49">
         <v>235.24828722421182</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-8.9934325780083935</v>
+        <v>-8.6141989211286685</v>
       </c>
       <c r="B50">
-        <v>-5.3577462803629183</v>
+        <v>-5.8748272315787764</v>
       </c>
       <c r="C50">
         <v>235.24828722421182</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-8.5460520818967964</v>
+        <v>-8.1828440666520521</v>
       </c>
       <c r="B51">
-        <v>-4.7806816850976261</v>
+        <v>-5.28753598266094</v>
       </c>
       <c r="C51">
         <v>235.24828722421182</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-8.0916605346501171</v>
+        <v>-7.744622931176516</v>
       </c>
       <c r="B52">
-        <v>-4.2104358399099331</v>
+        <v>-4.7063347016324055</v>
       </c>
       <c r="C52">
         <v>235.24828722421182</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-7.6308031288737537</v>
+        <v>-7.3002481475078191</v>
       </c>
       <c r="B53">
-        <v>-3.6464785058886209</v>
+        <v>-4.1305913271335246</v>
       </c>
       <c r="C53">
         <v>235.24828722421182</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-7.164025057173105</v>
+        <v>-6.8504323484517124</v>
       </c>
       <c r="B54">
-        <v>-3.0882794441224619</v>
+        <v>-3.5596737978046429</v>
       </c>
       <c r="C54">
         <v>235.24828722421182</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.6917515005344894</v>
+        <v>-6.3957284643169805</v>
       </c>
       <c r="B55">
-        <v>-2.5354251356073121</v>
+        <v>-2.9930916985540987</v>
       </c>
       <c r="C55">
         <v>235.24828722421182</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-6.2139275934678659</v>
+        <v>-5.9360506154244872</v>
       </c>
       <c r="B56">
-        <v>-1.9879689409673067</v>
+        <v>-2.430921199362162</v>
       </c>
       <c r="C56">
         <v>235.24828722421182</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.7303784588641138</v>
+        <v>-5.4711532195981345</v>
       </c>
       <c r="B57">
-        <v>-1.4460809407336583</v>
+        <v>-1.8733801164770911</v>
       </c>
       <c r="C57">
         <v>235.24828722421182</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-5.240929219614114</v>
+        <v>-5.0007906946618155</v>
       </c>
       <c r="B58">
-        <v>-0.90993121543757893</v>
+        <v>-1.3206862661471455</v>
       </c>
       <c r="C58">
         <v>235.24828722421182</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.7454263535956738</v>
+        <v>-4.5247473309884514</v>
       </c>
       <c r="B59">
-        <v>-0.37966907635385339</v>
+        <v>-0.77303096951145189</v>
       </c>
       <c r="C59">
         <v>235.24828722421182</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.2438017586343486</v>
+        <v>-4.042926909147079</v>
       </c>
       <c r="B60">
-        <v>0.14463924226841909</v>
+        <v>-0.23049956727264695</v>
       </c>
       <c r="C60">
         <v>235.24828722421182</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.7360086875426188</v>
+        <v>-3.5552630822557565</v>
       </c>
       <c r="B61">
-        <v>0.662948275436569</v>
+        <v>0.30684909497576912</v>
       </c>
       <c r="C61">
         <v>235.24828722421182</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.2220003931329741</v>
+        <v>-3.0616895034325484</v>
       </c>
       <c r="B62">
-        <v>1.1752125581579218</v>
+        <v>0.8389561716402878</v>
       </c>
       <c r="C62">
         <v>235.24828722421182</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.701880878846703</v>
+        <v>-2.5623433332896859</v>
       </c>
       <c r="B63">
-        <v>1.6815332412384929</v>
+        <v>1.3659433157269958</v>
       </c>
       <c r="C63">
         <v>235.24828722421182</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.1763571506402943</v>
+        <v>-2.0581757624160764</v>
       </c>
       <c r="B64">
-        <v>2.1825979386790659</v>
+        <v>1.8886541746403582</v>
       </c>
       <c r="C64">
         <v>235.24828722421182</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.6462869650990393</v>
+        <v>-1.5503414888947973</v>
       </c>
       <c r="B65">
-        <v>2.6792408802791146</v>
+        <v>2.4081128943844319</v>
       </c>
       <c r="C65">
         <v>235.24828722421182</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.1125280788082281</v>
+        <v>-1.0399952108089252</v>
       </c>
       <c r="B66">
-        <v>3.17229629583811</v>
+        <v>2.9253436209632753</v>
       </c>
       <c r="C66">
         <v>235.24828722421182</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.57481062503208369</v>
+        <v>-0.52677960619762354</v>
       </c>
       <c r="B67">
-        <v>3.6615017206000458</v>
+        <v>3.4400294318291542</v>
       </c>
       <c r="C67">
         <v>235.24828722421182</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.028354243750551827</v>
+        <v>-0.0042892729244041992</v>
       </c>
       <c r="B68">
-        <v>4.1422079115869916</v>
+        <v>3.9464891302271687</v>
       </c>
       <c r="C68">
         <v>235.24828722421182</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>0.53055505242457324</v>
+        <v>0.532448862757569</v>
       </c>
       <c r="B69">
-        <v>4.610802749688192</v>
+        <v>4.44031190637046</v>
       </c>
       <c r="C69">
         <v>235.24828722421182</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>1.096855267069818</v>
+        <v>1.0766304808608684</v>
       </c>
       <c r="B70">
-        <v>5.072209389483513</v>
+        <v>4.92753277255149</v>
       </c>
       <c r="C70">
         <v>235.24828722421182</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>1.6650276888400999</v>
+        <v>1.6208372612782613</v>
       </c>
       <c r="B71">
-        <v>5.5317951735707291</v>
+        <v>5.4147313213113595</v>
       </c>
       <c r="C71">
         <v>235.24828722421182</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2.2365027305155651</v>
+        <v>2.166972277157563</v>
       </c>
       <c r="B72">
-        <v>5.9881689229286534</v>
+        <v>5.9002196441064205</v>
       </c>
       <c r="C72">
         <v>235.24828722421182</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2.8136388545893154</v>
+        <v>2.718182430414219</v>
       </c>
       <c r="B73">
-        <v>6.439036863628381</v>
+        <v>6.3812066329673254</v>
       </c>
       <c r="C73">
         <v>235.24828722421182</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>3.3955575982810484</v>
+        <v>3.2732685447791758</v>
       </c>
       <c r="B74">
-        <v>6.8852533637291309</v>
+        <v>6.858755883306686</v>
       </c>
       <c r="C74">
         <v>235.24828722421182</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>3.9805560426662443</v>
+        <v>3.8299237309959917</v>
       </c>
       <c r="B75">
-        <v>7.3284746340222648</v>
+        <v>7.33491346365827</v>
       </c>
       <c r="C75">
         <v>235.24828722421182</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>4.5668703695168906</v>
+        <v>4.3857563260431887</v>
       </c>
       <c r="B76">
-        <v>7.7704161142396284</v>
+        <v>7.8118006316585111</v>
       </c>
       <c r="C76">
         <v>235.24828722421182</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>5.152879005241755</v>
+        <v>4.93856388799219</v>
       </c>
       <c r="B77">
-        <v>8.2126549010016863</v>
+        <v>8.2913708175013046</v>
       </c>
       <c r="C77">
         <v>235.24828722421182</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>5.7375902541001862</v>
+        <v>5.48698563305107</v>
       </c>
       <c r="B78">
-        <v>8.6561554895429218</v>
+        <v>8.7748309525077541</v>
       </c>
       <c r="C78">
         <v>235.24828722421182</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>6.3192495301589817</v>
+        <v>6.0286355004736061</v>
       </c>
       <c r="B79">
-        <v>9.1026243405263187</v>
+        <v>9.2642973254415661</v>
       </c>
       <c r="C79">
         <v>235.24828722421182</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>6.89471146427705</v>
+        <v>6.559257865641392</v>
       </c>
       <c r="B80">
-        <v>9.5551205510347081</v>
+        <v>9.7635444129486935</v>
       </c>
       <c r="C80">
         <v>235.24828722421182</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>7.45609313981189</v>
+        <v>7.068237514738585</v>
       </c>
       <c r="B81">
-        <v>10.021310822883846</v>
+        <v>10.281987255177764</v>
       </c>
       <c r="C81">
         <v>235.24828722421182</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>7.8593447057755306</v>
+        <v>7.3622491622336863</v>
       </c>
       <c r="B82">
-        <v>10.641293967746487</v>
+        <v>10.991093460469035</v>
       </c>
       <c r="C82">
         <v>235.24828722421182</v>
